--- a/output/北塩原村_令和8年法改正の反映.xlsx
+++ b/output/北塩原村_令和8年法改正の反映.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>公布から2年6月は令和11年1月24日までであり、第8期計画の期間（令和9年4月1日から令和12年3月31日まで）の内側に収まる。「本計画の期間中に施行されます」に直した</t>
+          <t>公布は令和8年6月であり、そこから2年6月は令和10年12月までである。第8期計画の期間（令和9年4月1日から令和12年3月31日まで）の内側に収まる。日まで断定せず月で押さえている（「超えない範囲内」の起算の取り方で末日が1日動くため）。いずれの取り方でも計画期間の内側であることは変わらない。「本計画の期間中に施行されます」に直した</t>
         </is>
       </c>
     </row>
